--- a/data/trans_dic/P79$hipoteca_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P79$hipoteca_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,82</t>
+          <t>0,08; 1,22</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,39</t>
+          <t>0,32; 3,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,75</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,85</t>
+          <t>0,32; 1,89</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,42</t>
+          <t>0,14; 1,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,2</t>
+          <t>0,38; 1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,02</t>
+          <t>0,32; 1,06</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,82</t>
+          <t>1,94; 4,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,06</t>
+          <t>1,21; 3,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,02</t>
+          <t>1,83; 3,31</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,29</t>
+          <t>0,69; 1,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,91</t>
+          <t>0,51; 0,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,0</t>
+          <t>0,66; 1,11</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2460</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 10446</t>
+          <t>0; 7084</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3215</t>
+          <t>0; 2476</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>528; 10669</t>
+          <t>501; 7569</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3391</t>
+          <t>0; 3466</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3371</t>
+          <t>0; 3522</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>865</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1512</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>0; 4468</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3155</t>
+          <t>0; 2967</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4884</t>
+          <t>0; 5535</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6456</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1094; 10095</t>
+          <t>1146; 10684</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>559; 6681</t>
+          <t>0; 7065</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2390; 12559</t>
+          <t>2392; 14090</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 6341</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4780</t>
+          <t>0; 5667</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8790</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>811; 8341</t>
+          <t>963; 8621</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1513; 9831</t>
+          <t>2775; 10939</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3456; 14393</t>
+          <t>4467; 15038</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>39324</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8489; 34968</t>
+          <t>15136; 36293</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8816; 21159</t>
+          <t>9670; 24052</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19112; 48528</t>
+          <t>29005; 52384</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>19735; 43492</t>
+          <t>23716; 48897</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15615; 31908</t>
+          <t>18330; 35539</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40136; 68994</t>
+          <t>46623; 77646</t>
         </is>
       </c>
     </row>
